--- a/sheets/조재수대금교본/검수/가을 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/가을 사랑.xlsx
@@ -4484,8 +4484,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="C6" s="26"/>
@@ -4503,27 +4502,21 @@
         </is>
       </c>
       <c r="G6" s="26"/>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H6" s="21"/>
       <c r="I6" s="26"/>
       <c r="J6" s="21"/>
       <c r="K6" s="26"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="M6" s="26"/>
       <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太
-仲
-‹</t>
+仲</t>
         </is>
       </c>
       <c r="O6" s="26"/>
@@ -4644,17 +4637,9 @@
         </is>
       </c>
       <c r="C9" s="25"/>
-      <c r="D9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D9" s="21"/>
       <c r="E9" s="25"/>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="25"/>
       <c r="H9" s="21" t="inlineStr">
         <is>
@@ -4668,37 +4653,20 @@
         </is>
       </c>
       <c r="K9" s="25"/>
-      <c r="L9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L9" s="21"/>
       <c r="M9" s="25"/>
-      <c r="N9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N9" s="21"/>
       <c r="O9" s="25"/>
-      <c r="P9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P9" s="21"/>
       <c r="Q9" s="25"/>
-      <c r="R9" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R9" s="21"/>
       <c r="S9" s="25"/>
     </row>
     <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C10" s="26"/>
@@ -4910,8 +4878,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㅂ
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C14" s="26"/>
@@ -4993,7 +4960,7 @@
       <c r="G15" s="22"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲ʒ
+          <t xml:space="preserve">仲
 –</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/가을 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/가을 사랑.xlsx
@@ -4878,7 +4878,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㅂ</t>
         </is>
       </c>
       <c r="C14" s="26"/>
@@ -4960,7 +4960,7 @@
       <c r="G15" s="22"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
+          <t xml:space="preserve">仲ʒ
 –</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/가을 사랑.xlsx
+++ b/sheets/조재수대금교본/검수/가을 사랑.xlsx
@@ -4276,30 +4276,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="10.71" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="10.71" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="81.63" customHeight="true">
+    <row r="2" ht="71.43" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="91.25" customHeight="true">
+    <row r="3" ht="79.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
       </c>
       <c r="S3" s="24"/>
     </row>
-    <row r="4" ht="91.25" customHeight="true">
+    <row r="4" ht="79.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4416,7 +4416,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="25"/>
     </row>
-    <row r="5" ht="91.25" customHeight="true">
+    <row r="5" ht="79.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="S5" s="25"/>
     </row>
-    <row r="6" ht="91.25" customHeight="true">
+    <row r="6" ht="79.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
       </c>
       <c r="S6" s="26"/>
     </row>
-    <row r="7" ht="91.25" customHeight="true">
+    <row r="7" ht="79.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="91.25" customHeight="true">
+    <row r="8" ht="79.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       <c r="R8" s="21"/>
       <c r="S8" s="25"/>
     </row>
-    <row r="9" ht="91.25" customHeight="true">
+    <row r="9" ht="79.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="25"/>
     </row>
-    <row r="10" ht="91.25" customHeight="true">
+    <row r="10" ht="79.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="S10" s="26"/>
     </row>
-    <row r="11" ht="91.25" customHeight="true">
+    <row r="11" ht="79.8" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="91.25" customHeight="true">
+    <row r="12" ht="79.8" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="25"/>
     </row>
-    <row r="13" ht="91.25" customHeight="true">
+    <row r="13" ht="79.8" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
       </c>
       <c r="S13" s="25"/>
     </row>
-    <row r="14" ht="91.25" customHeight="true">
+    <row r="14" ht="79.8" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="S14" s="26"/>
     </row>
-    <row r="15" ht="91.25" customHeight="true">
+    <row r="15" ht="79.8" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="91.25" customHeight="true">
+    <row r="16" ht="79.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -5017,7 +5017,7 @@
       <c r="R16" s="21"/>
       <c r="S16" s="25"/>
     </row>
-    <row r="17" ht="91.25" customHeight="true">
+    <row r="17" ht="79.8" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -5038,7 +5038,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="25"/>
     </row>
-    <row r="18" ht="91.25" customHeight="true">
+    <row r="18" ht="79.8" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5108,6 +5108,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="56"/>
 </worksheet>
 </file>